--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/25,06,26 Останкино СЫР/Дв. 22.06.2026 Останкино Сыр Бердянск.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/25,06,26 Останкино СЫР/Дв. 22.06.2026 Останкино Сыр Бердянск.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\Заказы на отправку и сортировку\Останкино\Останкино исходники\СЫРЫ\Бердянск\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\25,06,26 Останкино СЫР\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D67F42-EB50-4B2F-A1AC-A95852C4E343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9DE5EC-952B-4952-8F32-34F58FD5B172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="100">
   <si>
     <t>Ведомость по товарам на складах</t>
   </si>
@@ -315,9 +315,6 @@
     <t>7216 СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам. ОСТАНКИНО</t>
   </si>
   <si>
-    <t>итого</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -329,6 +326,9 @@
   <si>
     <t>блины</t>
   </si>
+  <si>
+    <t>заказ</t>
+  </si>
 </sst>
 </file>
 
@@ -338,7 +338,7 @@
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <name val="Arial"/>
@@ -375,6 +375,20 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -524,7 +538,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -579,6 +593,15 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -5130,7 +5153,7 @@
     <col min="11" max="11" width="1" customWidth="1"/>
     <col min="12" max="16" width="6.83203125" customWidth="1"/>
     <col min="17" max="17" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" style="25" customWidth="1"/>
     <col min="19" max="19" width="9.5" customWidth="1"/>
     <col min="20" max="20" width="8.83203125" customWidth="1"/>
     <col min="21" max="21" width="9.5" bestFit="1" customWidth="1"/>
@@ -5141,13 +5164,17 @@
     <col min="31" max="43" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1" spans="1:30" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R1" s="24"/>
+    </row>
     <row r="2" spans="1:30" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:30" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R3" s="24"/>
+    </row>
     <row r="4" spans="1:30" ht="13.15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>1</v>
@@ -5178,7 +5205,9 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:30" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:30" s="1" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R7" s="24"/>
+    </row>
     <row r="8" spans="1:30" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>6</v>
@@ -5222,7 +5251,7 @@
         <v>80</v>
       </c>
       <c r="R8" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="S8" s="14" t="s">
         <v>81</v>
@@ -5263,7 +5292,7 @@
     </row>
     <row r="9" spans="1:30" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -5297,7 +5326,9 @@
       <c r="Q9" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="R9" s="15"/>
+      <c r="R9" s="26" t="s">
+        <v>92</v>
+      </c>
       <c r="S9" s="15"/>
       <c r="T9" s="15"/>
       <c r="U9" s="15"/>
@@ -5319,15 +5350,15 @@
         <v>92</v>
       </c>
       <c r="AC9" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD9" s="15" t="s">
         <v>97</v>
-      </c>
-      <c r="AD9" s="15" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="19"/>
@@ -5375,9 +5406,9 @@
         <f t="shared" si="0"/>
         <v>3901.2489999999998</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="27">
         <f t="shared" si="0"/>
-        <v>3901.2489999999998</v>
+        <v>3813.2489999999998</v>
       </c>
       <c r="S10" s="16">
         <f t="shared" si="0"/>
@@ -5409,7 +5440,7 @@
       </c>
       <c r="AC10" s="16">
         <f>SUM(AC11:AC451)</f>
-        <v>1005.7409999999998</v>
+        <v>979.34099999999967</v>
       </c>
       <c r="AD10" s="16">
         <f>SUM(AD11:AD451)</f>
@@ -5467,7 +5498,7 @@
         <f>20*P11-G11-N11-O11</f>
         <v>103.88600000000002</v>
       </c>
-      <c r="R11" s="18">
+      <c r="R11" s="28">
         <f>Q11</f>
         <v>103.88600000000002</v>
       </c>
@@ -5560,7 +5591,7 @@
         <v>6.6</v>
       </c>
       <c r="Q12" s="18"/>
-      <c r="R12" s="18">
+      <c r="R12" s="28">
         <f t="shared" ref="R12:R68" si="3">Q12</f>
         <v>0</v>
       </c>
@@ -5655,7 +5686,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="Q13" s="18"/>
-      <c r="R13" s="18">
+      <c r="R13" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5749,7 +5780,7 @@
         <v>5.9207999999999998</v>
       </c>
       <c r="Q14" s="18"/>
-      <c r="R14" s="18">
+      <c r="R14" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5841,13 +5872,13 @@
         <v>2</v>
       </c>
       <c r="Q15" s="18"/>
-      <c r="R15" s="18">
+      <c r="R15" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S15" s="18"/>
       <c r="T15" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U15" s="17">
         <f t="shared" si="4"/>
@@ -5936,13 +5967,13 @@
         <v>3.6292</v>
       </c>
       <c r="Q16" s="18"/>
-      <c r="R16" s="18">
+      <c r="R16" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S16" s="18"/>
       <c r="T16" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U16" s="17">
         <f t="shared" si="4"/>
@@ -6028,13 +6059,13 @@
         <v>1.3</v>
       </c>
       <c r="Q17" s="18"/>
-      <c r="R17" s="18">
+      <c r="R17" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S17" s="18"/>
       <c r="T17" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U17" s="17">
         <f t="shared" si="4"/>
@@ -6122,13 +6153,13 @@
         <v>3.4</v>
       </c>
       <c r="Q18" s="18"/>
-      <c r="R18" s="18">
+      <c r="R18" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S18" s="18"/>
       <c r="T18" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U18" s="17">
         <f t="shared" si="4"/>
@@ -6222,13 +6253,12 @@
         <f t="shared" ref="Q19:Q67" si="9">20*P19-G19-N19-O19</f>
         <v>84</v>
       </c>
-      <c r="R19" s="18">
-        <f t="shared" si="3"/>
-        <v>84</v>
+      <c r="R19" s="28">
+        <v>0</v>
       </c>
       <c r="S19" s="18"/>
       <c r="T19" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U19" s="17">
         <f t="shared" si="4"/>
@@ -6261,7 +6291,7 @@
       </c>
       <c r="AC19" s="17">
         <f t="shared" si="7"/>
-        <v>25.2</v>
+        <v>0</v>
       </c>
       <c r="AD19" s="17">
         <f t="shared" si="8"/>
@@ -6316,13 +6346,12 @@
         <v>15.4</v>
       </c>
       <c r="Q20" s="18"/>
-      <c r="R20" s="18">
-        <f t="shared" si="3"/>
+      <c r="R20" s="28">
         <v>0</v>
       </c>
       <c r="S20" s="18"/>
       <c r="T20" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U20" s="17">
         <f t="shared" si="4"/>
@@ -6410,13 +6439,13 @@
         <v>11</v>
       </c>
       <c r="Q21" s="18"/>
-      <c r="R21" s="18">
+      <c r="R21" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S21" s="18"/>
       <c r="T21" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U21" s="17">
         <f t="shared" si="4"/>
@@ -6507,13 +6536,12 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="R22" s="18">
-        <f t="shared" si="3"/>
-        <v>4</v>
+      <c r="R22" s="28">
+        <v>0</v>
       </c>
       <c r="S22" s="18"/>
       <c r="T22" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U22" s="17">
         <f t="shared" si="4"/>
@@ -6546,7 +6574,7 @@
       </c>
       <c r="AC22" s="17">
         <f t="shared" si="7"/>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="17">
         <f t="shared" si="8"/>
@@ -6601,13 +6629,13 @@
         <v>7.8</v>
       </c>
       <c r="Q23" s="18"/>
-      <c r="R23" s="18">
+      <c r="R23" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S23" s="18"/>
       <c r="T23" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U23" s="17">
         <f t="shared" si="4"/>
@@ -6695,13 +6723,13 @@
         <v>2.6</v>
       </c>
       <c r="Q24" s="18"/>
-      <c r="R24" s="18">
+      <c r="R24" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S24" s="18"/>
       <c r="T24" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U24" s="17">
         <f t="shared" si="4"/>
@@ -6791,7 +6819,7 @@
         <v>1.6</v>
       </c>
       <c r="Q25" s="18"/>
-      <c r="R25" s="18">
+      <c r="R25" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6885,7 +6913,7 @@
         <v>21</v>
       </c>
       <c r="Q26" s="18"/>
-      <c r="R26" s="18">
+      <c r="R26" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6985,7 +7013,7 @@
         <f t="shared" si="9"/>
         <v>95</v>
       </c>
-      <c r="R27" s="18">
+      <c r="R27" s="28">
         <f t="shared" si="3"/>
         <v>95</v>
       </c>
@@ -7087,7 +7115,7 @@
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="R28" s="18">
+      <c r="R28" s="28">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
@@ -7186,7 +7214,7 @@
         <v>36.4</v>
       </c>
       <c r="Q29" s="18"/>
-      <c r="R29" s="18">
+      <c r="R29" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7279,7 +7307,7 @@
         <v>3.8</v>
       </c>
       <c r="Q30" s="18"/>
-      <c r="R30" s="18">
+      <c r="R30" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7378,7 +7406,7 @@
         <v>8.4</v>
       </c>
       <c r="Q31" s="18"/>
-      <c r="R31" s="18">
+      <c r="R31" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7468,7 +7496,7 @@
         <v>5.4</v>
       </c>
       <c r="Q32" s="18"/>
-      <c r="R32" s="18">
+      <c r="R32" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7555,7 +7583,7 @@
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="R33" s="18">
+      <c r="R33" s="28">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
@@ -7650,7 +7678,7 @@
         <f t="shared" si="9"/>
         <v>1519</v>
       </c>
-      <c r="R34" s="18">
+      <c r="R34" s="28">
         <f t="shared" si="3"/>
         <v>1519</v>
       </c>
@@ -7744,7 +7772,7 @@
         <v>42</v>
       </c>
       <c r="Q35" s="18"/>
-      <c r="R35" s="18">
+      <c r="R35" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7841,7 +7869,7 @@
         <v>0.2</v>
       </c>
       <c r="Q36" s="18"/>
-      <c r="R36" s="18">
+      <c r="R36" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7934,7 +7962,7 @@
         <v>1</v>
       </c>
       <c r="Q37" s="18"/>
-      <c r="R37" s="18">
+      <c r="R37" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8031,7 +8059,7 @@
         <v>0.8</v>
       </c>
       <c r="Q38" s="18"/>
-      <c r="R38" s="18">
+      <c r="R38" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8123,7 +8151,7 @@
         <v>0</v>
       </c>
       <c r="Q39" s="18"/>
-      <c r="R39" s="18">
+      <c r="R39" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8215,7 +8243,7 @@
         <v>0</v>
       </c>
       <c r="Q40" s="18"/>
-      <c r="R40" s="18">
+      <c r="R40" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8307,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="Q41" s="18"/>
-      <c r="R41" s="18">
+      <c r="R41" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8404,7 +8432,7 @@
         <v>0</v>
       </c>
       <c r="Q42" s="18"/>
-      <c r="R42" s="18">
+      <c r="R42" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8504,7 +8532,7 @@
         <f t="shared" si="9"/>
         <v>189</v>
       </c>
-      <c r="R43" s="18">
+      <c r="R43" s="28">
         <f t="shared" si="3"/>
         <v>189</v>
       </c>
@@ -8594,7 +8622,7 @@
         <v>2</v>
       </c>
       <c r="Q44" s="18"/>
-      <c r="R44" s="18">
+      <c r="R44" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8689,7 +8717,7 @@
         <f t="shared" si="9"/>
         <v>94</v>
       </c>
-      <c r="R45" s="18">
+      <c r="R45" s="28">
         <f t="shared" si="3"/>
         <v>94</v>
       </c>
@@ -8788,7 +8816,7 @@
         <f t="shared" si="9"/>
         <v>71</v>
       </c>
-      <c r="R46" s="18">
+      <c r="R46" s="28">
         <f t="shared" si="3"/>
         <v>71</v>
       </c>
@@ -8885,7 +8913,7 @@
         <v>19.8</v>
       </c>
       <c r="Q47" s="18"/>
-      <c r="R47" s="18">
+      <c r="R47" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8982,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="18"/>
-      <c r="R48" s="18">
+      <c r="R48" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9084,7 +9112,7 @@
         <f t="shared" si="9"/>
         <v>230</v>
       </c>
-      <c r="R49" s="18">
+      <c r="R49" s="28">
         <f t="shared" si="3"/>
         <v>230</v>
       </c>
@@ -9183,7 +9211,7 @@
         <v>24.4</v>
       </c>
       <c r="Q50" s="18"/>
-      <c r="R50" s="18">
+      <c r="R50" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9285,7 +9313,7 @@
         <f t="shared" si="9"/>
         <v>478</v>
       </c>
-      <c r="R51" s="18">
+      <c r="R51" s="28">
         <f t="shared" si="3"/>
         <v>478</v>
       </c>
@@ -9373,7 +9401,7 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="R52" s="18">
+      <c r="R52" s="28">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -9454,7 +9482,7 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="R53" s="18">
+      <c r="R53" s="28">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -9549,7 +9577,7 @@
         <f t="shared" si="9"/>
         <v>157</v>
       </c>
-      <c r="R54" s="18">
+      <c r="R54" s="28">
         <f t="shared" si="3"/>
         <v>157</v>
       </c>
@@ -9639,7 +9667,7 @@
         <v>4.6415999999999995</v>
       </c>
       <c r="Q55" s="18"/>
-      <c r="R55" s="18">
+      <c r="R55" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9729,7 +9757,7 @@
         <v>1.9647999999999999</v>
       </c>
       <c r="Q56" s="18"/>
-      <c r="R56" s="18">
+      <c r="R56" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9825,7 +9853,7 @@
         <v>5.2435999999999998</v>
       </c>
       <c r="Q57" s="18"/>
-      <c r="R57" s="18">
+      <c r="R57" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9912,7 +9940,7 @@
         <v>2.4143999999999997</v>
       </c>
       <c r="Q58" s="18"/>
-      <c r="R58" s="18">
+      <c r="R58" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -10011,7 +10039,7 @@
         <v>34</v>
       </c>
       <c r="Q59" s="18"/>
-      <c r="R59" s="18">
+      <c r="R59" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -10113,7 +10141,7 @@
         <f t="shared" si="9"/>
         <v>390</v>
       </c>
-      <c r="R60" s="18">
+      <c r="R60" s="28">
         <f t="shared" si="3"/>
         <v>390</v>
       </c>
@@ -10211,7 +10239,7 @@
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="R61" s="18">
+      <c r="R61" s="28">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
@@ -10311,7 +10339,7 @@
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="R62" s="18">
+      <c r="R62" s="28">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
@@ -10410,7 +10438,7 @@
         <f t="shared" si="9"/>
         <v>45</v>
       </c>
-      <c r="R63" s="18">
+      <c r="R63" s="28">
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
@@ -10508,7 +10536,7 @@
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="R64" s="18">
+      <c r="R64" s="28">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
@@ -10606,7 +10634,7 @@
         <f t="shared" si="9"/>
         <v>235.125</v>
       </c>
-      <c r="R65" s="18">
+      <c r="R65" s="28">
         <f t="shared" si="3"/>
         <v>235.125</v>
       </c>
@@ -10702,7 +10730,7 @@
         <f t="shared" si="9"/>
         <v>59</v>
       </c>
-      <c r="R66" s="18">
+      <c r="R66" s="28">
         <f t="shared" si="3"/>
         <v>59</v>
       </c>
@@ -10792,7 +10820,7 @@
         <f t="shared" si="9"/>
         <v>19.238</v>
       </c>
-      <c r="R67" s="18">
+      <c r="R67" s="28">
         <f t="shared" si="3"/>
         <v>19.238</v>
       </c>
@@ -10877,7 +10905,7 @@
         <v>29</v>
       </c>
       <c r="Q68" s="18"/>
-      <c r="R68" s="18">
+      <c r="R68" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
